--- a/AAII_Financials/Yearly/PBCRY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PBCRY_YR_FIN.xlsx
@@ -1781,10 +1781,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1282800</v>
+        <v>1282700</v>
       </c>
       <c r="E45" s="3">
-        <v>1403400</v>
+        <v>1401900</v>
       </c>
       <c r="F45" s="3">
         <v>1607100</v>
@@ -1814,10 +1814,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9441900</v>
+        <v>9441800</v>
       </c>
       <c r="E46" s="3">
-        <v>8562400</v>
+        <v>8560900</v>
       </c>
       <c r="F46" s="3">
         <v>17381000</v>
@@ -2012,10 +2012,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>539200</v>
+        <v>539300</v>
       </c>
       <c r="E52" s="3">
-        <v>444100</v>
+        <v>445500</v>
       </c>
       <c r="F52" s="3">
         <v>331000</v>
